--- a/test/ejemplo/planilla-ejemplo.xlsx
+++ b/test/ejemplo/planilla-ejemplo.xlsx
@@ -123,23 +123,18 @@
     </row>
     <row r="7">
       <c r="C7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>45931</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="G7">
-        <v>18.46</v>
+        <v>23.81</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -149,112 +144,117 @@
     </row>
     <row r="8">
       <c r="C8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <v>45931</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">regalos</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G8">
-        <v>2031.52</v>
+        <v>70.54</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>45931</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t xml:space="preserve">entretenimiento</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>42.84</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45931</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gastos fijos</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>109.12</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet+celular</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45931</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gastos fijos</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>102.4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45931</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
-      <c r="G9">
-        <v>23.22</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
-        <v>45931</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">supermercado</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>48.89</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1">
-        <v>45931</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>82.46</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>16</v>
-      </c>
-      <c r="D12" s="1">
-        <v>45931</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
       <c r="G12">
-        <v>102.4</v>
+        <v>24.02</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -264,18 +264,18 @@
     </row>
     <row r="13">
       <c r="C13">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1">
         <v>45931</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G13">
-        <v>30.68</v>
+        <v>90.17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -284,45 +284,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coruña</t>
-        </is>
-      </c>
       <c r="C14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
         <v>45931</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G14">
-        <v>215.06</v>
+        <v>23.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="C15">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1">
         <v>45931</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G15">
-        <v>23</v>
+        <v>67.93</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -331,24 +326,19 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luz</t>
-        </is>
-      </c>
       <c r="C16">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1">
         <v>45931</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G16">
-        <v>96.17</v>
+        <v>44.84</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -358,23 +348,18 @@
     </row>
     <row r="17">
       <c r="C17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1">
         <v>45931</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G17">
-        <v>17.86</v>
+        <v>91.37</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -385,22 +370,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Praga</t>
+          <t xml:space="preserve">Gas</t>
         </is>
       </c>
       <c r="C18">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1">
         <v>45931</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G18">
-        <v>244.21</v>
+        <v>59.46</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -410,65 +395,70 @@
     </row>
     <row r="19">
       <c r="C19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1">
         <v>45931</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G19">
-        <v>8.91</v>
+        <v>12.34</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="C20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
         <v>45931</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t xml:space="preserve">gastos fijos</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>100.2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1">
+        <v>45931</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">salud</t>
         </is>
       </c>
-      <c r="G20">
-        <v>24.88</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1">
-        <v>45931</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
       <c r="G21">
-        <v>106.86</v>
+        <v>67.02</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -478,18 +468,18 @@
     </row>
     <row r="22">
       <c r="C22">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>45931</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G22">
-        <v>5.01</v>
+        <v>29.22</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -499,39 +489,39 @@
     </row>
     <row r="23">
       <c r="C23">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1">
         <v>45931</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G23">
-        <v>67.02</v>
+        <v>77.63</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="C24">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1">
         <v>45931</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G24">
-        <v>72.97</v>
+        <v>71.84095981849403</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -541,18 +531,18 @@
     </row>
     <row r="25">
       <c r="C25">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D25" s="1">
         <v>45931</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G25">
-        <v>37.43</v>
+        <v>28.201582620014243</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -561,24 +551,19 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luz</t>
-        </is>
-      </c>
       <c r="C26">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1">
         <v>45931</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G26">
-        <v>129.32</v>
+        <v>51.70155050545071</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -588,23 +573,18 @@
     </row>
     <row r="27">
       <c r="C27">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D27" s="1">
         <v>45931</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G27">
-        <v>39.01</v>
+        <v>10.77</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -614,96 +594,91 @@
     </row>
     <row r="28">
       <c r="C28">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1">
+        <v>45931</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transporte</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>32.29</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45931</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transporte</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30">
         <v>23</v>
       </c>
-      <c r="D28" s="1">
-        <v>45931</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">regalos</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>968.24</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>9</v>
-      </c>
-      <c r="D29" s="1">
-        <v>45931</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>112.88</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coruña</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>22</v>
-      </c>
       <c r="D30" s="1">
         <v>45931</v>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G30">
-        <v>116.81</v>
+        <v>48.56</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="C31">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1">
         <v>45931</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G31">
-        <v>6.36</v>
+        <v>30.25020886503635</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -713,49 +688,49 @@
     </row>
     <row r="32">
       <c r="C32">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D32" s="1">
         <v>45931</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G32">
-        <v>59.16</v>
+        <v>573.55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D33" s="1">
         <v>45931</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">regalos</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G33">
-        <v>881.25</v>
+        <v>58.56</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="C34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" s="1">
         <v>45931</v>
@@ -767,11 +742,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G34">
-        <v>19.51</v>
+        <v>33.675055694615025</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -781,60 +756,70 @@
     </row>
     <row r="35">
       <c r="C35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
         <v>45931</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">inversiones</t>
         </is>
       </c>
       <c r="G35">
-        <v>49.32</v>
+        <v>1336.84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C36">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D36" s="1">
         <v>45931</v>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G36">
-        <v>58.56</v>
+        <v>75.86</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="C37">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D37" s="1">
         <v>45931</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G37">
-        <v>20.21</v>
+        <v>49.08</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -844,18 +829,25 @@
     </row>
     <row r="38">
       <c r="C38">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D38" s="1">
         <v>45931</v>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>9.41</v>
+          <t xml:space="preserve">otros</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49,84</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -865,18 +857,18 @@
     </row>
     <row r="39">
       <c r="C39">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1">
         <v>45931</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G39">
-        <v>36.73</v>
+        <v>13.82</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -887,27 +879,22 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luz</t>
+          <t xml:space="preserve">Guanacaste</t>
         </is>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D40" s="1">
         <v>45931</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G40">
-        <v>58.67</v>
+        <v>161.25</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -916,19 +903,24 @@
       </c>
     </row>
     <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisboa</t>
+        </is>
+      </c>
       <c r="C41">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D41" s="1">
         <v>45931</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G41">
-        <v>62.5</v>
+        <v>184.86</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -938,18 +930,18 @@
     </row>
     <row r="42">
       <c r="C42">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1">
         <v>45931</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G42">
-        <v>18.48</v>
+        <v>88.0392492204156</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -958,19 +950,24 @@
       </c>
     </row>
     <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Psicóloga</t>
+        </is>
+      </c>
       <c r="C43">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D43" s="1">
         <v>45931</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G43">
-        <v>12.71</v>
+        <v>79.04</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -980,18 +977,23 @@
     </row>
     <row r="44">
       <c r="C44">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D44" s="1">
         <v>45931</v>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">OTROS</t>
         </is>
       </c>
       <c r="G44">
-        <v>57.65</v>
+        <v>68.33</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1001,44 +1003,39 @@
     </row>
     <row r="45">
       <c r="C45">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D45" s="1">
         <v>45931</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">inversiones</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G45">
-        <v>973.41</v>
+        <v>73.3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="C46">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D46" s="1">
         <v>45931</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G46">
-        <v>43.89</v>
+        <v>5.646959543529413</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1047,13 +1044,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C47">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D47" s="1">
         <v>45931</v>
@@ -1065,11 +1057,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G47">
-        <v>132.09</v>
+        <v>49.170156737868744</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1078,40 +1070,45 @@
       </c>
     </row>
     <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
       <c r="C48">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D48" s="1">
         <v>45931</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G48">
-        <v>34.92</v>
+        <v>68.27</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="C49">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1">
         <v>45931</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G49">
-        <v>8.15</v>
+        <v>20.13</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1121,7 +1118,7 @@
     </row>
     <row r="50">
       <c r="C50">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D50" s="1">
         <v>45931</v>
@@ -1133,63 +1130,68 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G50">
-        <v>31.59</v>
+        <v>1517.81</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D51" s="1">
         <v>45931</v>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G51">
-        <v>5.65</v>
+        <v>19.55</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="C52">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D52" s="1">
         <v>45931</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G52">
-        <v>55.3</v>
+        <v>26.92</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="C53">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D53" s="1">
         <v>45931</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>18.05</v>
+        <v>25.784088025700342</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -1210,18 +1212,18 @@
     </row>
     <row r="54">
       <c r="C54">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D54" s="1">
         <v>45931</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G54">
-        <v>10.36</v>
+        <v>28.29</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -1230,92 +1232,97 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Praga</t>
-        </is>
-      </c>
       <c r="C55">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D55" s="1">
         <v>45931</v>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G55">
-        <v>119.07</v>
+        <v>104.86</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="C56">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D56" s="1">
         <v>45931</v>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">inversiones</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G56">
-        <v>601.47</v>
+        <v>26.894147049120697</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="C57">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D57" s="1">
         <v>45931</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G57">
-        <v>57.38</v>
+        <v>680.72</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas</t>
+        </is>
+      </c>
       <c r="C58">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1">
         <v>45931</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G58">
-        <v>87.21</v>
+        <v>118.24</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -1325,18 +1332,23 @@
     </row>
     <row r="59">
       <c r="C59">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1">
         <v>45931</v>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G59">
-        <v>25.78</v>
+        <v>14.88</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -1346,18 +1358,18 @@
     </row>
     <row r="60">
       <c r="C60">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D60" s="1">
         <v>45931</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G60">
-        <v>82.28</v>
+        <v>43.15</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -1379,11 +1391,13 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G61">
-        <v>43.27</v>
+          <t xml:space="preserve">supermercado</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66,87</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -1392,28 +1406,23 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisboa</t>
-        </is>
-      </c>
       <c r="C62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" s="1">
         <v>45931</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G62">
-        <v>220.67</v>
+        <v>1257.05</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
@@ -1424,44 +1433,44 @@
         </is>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D63" s="1">
         <v>45931</v>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G63">
-        <v>26.57</v>
+        <v>96.75</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="C64">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D64" s="1">
         <v>45931</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENTRETENIMIENTO</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G64">
-        <v>47.09</v>
+        <v>61</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -1471,7 +1480,7 @@
     </row>
     <row r="65">
       <c r="C65">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D65" s="1">
         <v>45931</v>
@@ -1482,7 +1491,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>57.08</v>
+        <v>33.36</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -1491,13 +1500,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
       <c r="C66">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D66" s="1">
         <v>45931</v>
@@ -1509,11 +1513,13 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>135.8</v>
+          <t xml:space="preserve">otros</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35,68</t>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -1523,7 +1529,7 @@
     </row>
     <row r="67">
       <c r="C67">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D67" s="1">
         <v>45931</v>
@@ -1534,7 +1540,7 @@
         </is>
       </c>
       <c r="G67">
-        <v>82.3</v>
+        <v>89.3</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -1549,18 +1555,13 @@
       <c r="D68" s="1">
         <v>45931</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G68">
-        <v>5.15</v>
+        <v>29.85</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -1569,6 +1570,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet+celular</t>
+        </is>
+      </c>
       <c r="C69">
         <v>5</v>
       </c>
@@ -1577,53 +1583,53 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">trabajo</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G69">
-        <v>1257.05</v>
+        <v>57.66</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="C70">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D70" s="1">
         <v>45931</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G70">
-        <v>9.72</v>
+        <v>5.27</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="C71">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D71" s="1">
         <v>45931</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G71">
-        <v>9.02</v>
+        <v>83.99379137856596</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -1643,13 +1649,18 @@
       <c r="D72" s="1">
         <v>45931</v>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G72">
-        <v>21.58</v>
+        <v>89.21</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -1659,18 +1670,23 @@
     </row>
     <row r="73">
       <c r="C73">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D73" s="1">
         <v>45931</v>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G73">
-        <v>60.42</v>
+        <v>29.4</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -1680,23 +1696,18 @@
     </row>
     <row r="74">
       <c r="C74">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D74" s="1">
         <v>45931</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G74">
-        <v>12.35</v>
+        <v>82.84737232972279</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -1706,18 +1717,18 @@
     </row>
     <row r="75">
       <c r="C75">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" s="1">
         <v>45931</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G75">
-        <v>34.74</v>
+        <v>38.26</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -1727,18 +1738,18 @@
     </row>
     <row r="76">
       <c r="C76">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D76" s="1">
         <v>45931</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G76">
-        <v>29.85</v>
+        <v>13.56</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -1814,7 +1825,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D83" s="1">
         <v>45962</v>
@@ -1825,7 +1836,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>57.66</v>
+        <v>98.01</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -1835,23 +1846,18 @@
     </row>
     <row r="84">
       <c r="C84">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D84" s="1">
         <v>45962</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G84">
-        <v>75.92</v>
+        <v>61.47</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -1860,87 +1866,92 @@
       </c>
     </row>
     <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas</t>
+        </is>
+      </c>
       <c r="C85">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D85" s="1">
         <v>45962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G85">
-        <v>1957.85</v>
+        <v>36</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="C86">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D86" s="1">
         <v>45962</v>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G86">
+        <v>12.01</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87">
+        <v>20</v>
+      </c>
+      <c r="D87" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">regalos</t>
         </is>
       </c>
-      <c r="G86">
-        <v>1729.52</v>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="G87">
+        <v>1805.52</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
-      <c r="C87">
-        <v>9</v>
-      </c>
-      <c r="D87" s="1">
-        <v>45962</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G87">
-        <v>236.28</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="C88">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D88" s="1">
         <v>45962</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G88">
-        <v>84.64</v>
+        <v>26.27</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -1950,23 +1961,18 @@
     </row>
     <row r="89">
       <c r="C89">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D89" s="1">
         <v>45962</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G89">
-        <v>49.9</v>
+        <v>24.58</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -1976,18 +1982,23 @@
     </row>
     <row r="90">
       <c r="C90">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D90" s="1">
         <v>45962</v>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G90">
-        <v>14.31</v>
+        <v>14.1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -1997,18 +2008,18 @@
     </row>
     <row r="91">
       <c r="C91">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D91" s="1">
         <v>45962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G91">
-        <v>13.56</v>
+        <v>12.36</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -2018,23 +2029,18 @@
     </row>
     <row r="92">
       <c r="C92">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D92" s="1">
         <v>45962</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G92">
-        <v>19.66</v>
+        <v>15.2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -2044,39 +2050,44 @@
     </row>
     <row r="93">
       <c r="C93">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D93" s="1">
         <v>45962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G93">
-        <v>50.11</v>
+        <v>889.83</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="C94">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D94" s="1">
         <v>45962</v>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">TRANSPORTE</t>
         </is>
       </c>
       <c r="G94">
-        <v>31.61</v>
+        <v>82.14</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -2086,23 +2097,18 @@
     </row>
     <row r="95">
       <c r="C95">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D95" s="1">
         <v>45962</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G95">
-        <v>13.21</v>
+        <v>16.77</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -2112,44 +2118,39 @@
     </row>
     <row r="96">
       <c r="C96">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D96" s="1">
         <v>45962</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">regalos</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G96">
-        <v>1880.61</v>
+        <v>24.7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">i</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guanacaste</t>
-        </is>
-      </c>
       <c r="C97">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D97" s="1">
         <v>45962</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G97">
-        <v>31.4</v>
+        <v>35.35</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -2159,18 +2160,18 @@
     </row>
     <row r="98">
       <c r="C98">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D98" s="1">
         <v>45962</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G98">
-        <v>13.74</v>
+        <v>45.72</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -2179,24 +2180,19 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coruña</t>
-        </is>
-      </c>
       <c r="C99">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D99" s="1">
         <v>45962</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G99">
-        <v>174.65</v>
+        <v>74.63</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -2206,7 +2202,7 @@
     </row>
     <row r="100">
       <c r="C100">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D100" s="1">
         <v>45962</v>
@@ -2217,7 +2213,7 @@
         </is>
       </c>
       <c r="G100">
-        <v>81.9</v>
+        <v>20.47</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -2226,19 +2222,24 @@
       </c>
     </row>
     <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
       <c r="C101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" s="1">
         <v>45962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G101">
-        <v>77.42</v>
+        <v>221.06568465291787</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -2248,18 +2249,23 @@
     </row>
     <row r="102">
       <c r="C102">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D102" s="1">
         <v>45962</v>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G102">
-        <v>55.67</v>
+        <v>81.05577472413694</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -2268,45 +2274,45 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C103">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D103" s="1">
         <v>45962</v>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G103">
-        <v>76.64</v>
+        <v>1121.89</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="C104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D104" s="1">
         <v>45962</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G104">
-        <v>35.93</v>
+        <v>13.08</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -2315,24 +2321,24 @@
       </c>
     </row>
     <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guanacaste</t>
+        </is>
+      </c>
       <c r="C105">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D105" s="1">
         <v>45962</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G105">
-        <v>16.44</v>
+        <v>55.16</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -2342,18 +2348,18 @@
     </row>
     <row r="106">
       <c r="C106">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D106" s="1">
         <v>45962</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G106">
-        <v>16.77</v>
+        <v>45.5</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -2364,22 +2370,22 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roma</t>
+          <t xml:space="preserve">Luz</t>
         </is>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D107" s="1">
         <v>45962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G107">
-        <v>222</v>
+        <v>110.74</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -2389,18 +2395,18 @@
     </row>
     <row r="108">
       <c r="C108">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D108" s="1">
         <v>45962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G108">
-        <v>60.46</v>
+        <v>43.51</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -2410,39 +2416,39 @@
     </row>
     <row r="109">
       <c r="C109">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D109" s="1">
         <v>45962</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">inversiones</t>
         </is>
       </c>
       <c r="G109">
-        <v>86.42</v>
+        <v>1605.14</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="C110">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D110" s="1">
         <v>45962</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G110">
-        <v>45.81</v>
+        <v>23.66</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -2452,28 +2458,28 @@
     </row>
     <row r="111">
       <c r="C111">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D111" s="1">
         <v>45962</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G111">
-        <v>22.1</v>
+        <v>618.66</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="C112">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D112" s="1">
         <v>45962</v>
@@ -2485,11 +2491,11 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G112">
-        <v>48.2</v>
+        <v>38.96</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -2499,23 +2505,18 @@
     </row>
     <row r="113">
       <c r="C113">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D113" s="1">
         <v>45962</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G113">
-        <v>64.61</v>
+        <v>42.39319087816085</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -2525,75 +2526,70 @@
     </row>
     <row r="114">
       <c r="C114">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D114" s="1">
         <v>45962</v>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G114">
+        <v>24.229625711324452</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" s="1">
+        <v>45962</v>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t xml:space="preserve">detalle de ejemplo</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salud</t>
-        </is>
-      </c>
-      <c r="G114">
-        <v>14.29</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="C115">
-        <v>9</v>
-      </c>
-      <c r="D115" s="1">
-        <v>45962</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">trabajo</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G115">
-        <v>1121.89</v>
+        <v>40.88</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="C116">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D116" s="1">
         <v>45962</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G116">
-        <v>73.7</v>
+        <v>54.34</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -2603,18 +2599,18 @@
     </row>
     <row r="117">
       <c r="C117">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D117" s="1">
         <v>45962</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G117">
-        <v>50.14</v>
+        <v>37.44</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -2624,33 +2620,30 @@
     </row>
     <row r="118">
       <c r="C118">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D118" s="1">
         <v>45962</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>86.39</v>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="C119">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D119" s="1">
         <v>45962</v>
@@ -2661,28 +2654,28 @@
         </is>
       </c>
       <c r="G119">
-        <v>82.13</v>
+        <v>44.42</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="C120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D120" s="1">
         <v>45962</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G120">
-        <v>98.78</v>
+        <v>25.46</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -2692,18 +2685,23 @@
     </row>
     <row r="121">
       <c r="C121">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D121" s="1">
         <v>45962</v>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G121">
-        <v>43.51</v>
+        <v>59.631598021197874</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -2714,11 +2712,11 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internet+celular</t>
+          <t xml:space="preserve">Gas</t>
         </is>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D122" s="1">
         <v>45962</v>
@@ -2729,28 +2727,28 @@
         </is>
       </c>
       <c r="G122">
-        <v>115.57</v>
+        <v>110.94</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="C123">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D123" s="1">
         <v>45962</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G123">
-        <v>23.66</v>
+        <v>10</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -2759,24 +2757,24 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luz</t>
-        </is>
-      </c>
       <c r="C124">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D124" s="1">
         <v>45962</v>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G124">
-        <v>92.12</v>
+        <v>10.56</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -2785,24 +2783,24 @@
       </c>
     </row>
     <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Praga</t>
+        </is>
+      </c>
       <c r="C125">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D125" s="1">
         <v>45962</v>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G125">
-        <v>38.96</v>
+        <v>173.22</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -2812,18 +2810,20 @@
     </row>
     <row r="126">
       <c r="C126">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D126" s="1">
         <v>45962</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>46.76</v>
+          <t xml:space="preserve">otros</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61,5</t>
+        </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -2832,19 +2832,29 @@
       </c>
     </row>
     <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C127">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D127" s="1">
         <v>45962</v>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G127">
-        <v>68.68</v>
+        <v>201.67</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -2854,27 +2864,22 @@
     </row>
     <row r="128">
       <c r="C128">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D128" s="1">
         <v>45962</v>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">OTROS</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G128">
-        <v>262.69</v>
+        <v>18.72</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
@@ -2885,18 +2890,23 @@
         </is>
       </c>
       <c r="C129">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D129" s="1">
         <v>45962</v>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G129">
-        <v>90.13</v>
+        <v>29.75</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -2906,18 +2916,18 @@
     </row>
     <row r="130">
       <c r="C130">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D130" s="1">
         <v>45962</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G130">
-        <v>70.38</v>
+        <v>69.96</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -2927,91 +2937,86 @@
     </row>
     <row r="131">
       <c r="C131">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D131" s="1">
         <v>45962</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G131">
-        <v>79.81</v>
+        <v>59.19</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="C132">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D132" s="1">
         <v>45962</v>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G132">
-        <v>45.83</v>
+        <v>46.43</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisboa</t>
+        </is>
+      </c>
       <c r="C133">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D133" s="1">
         <v>45962</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t xml:space="preserve">viajes</t>
+        </is>
+      </c>
+      <c r="G133">
+        <v>99.99766145134235</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">salud</t>
         </is>
       </c>
-      <c r="G133">
-        <v>44.42</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Praga</t>
-        </is>
-      </c>
-      <c r="C134">
-        <v>2</v>
-      </c>
-      <c r="D134" s="1">
-        <v>45962</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
       <c r="G134">
-        <v>71.83</v>
+        <v>7.6</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
     </row>
     <row r="135">
       <c r="C135">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D135" s="1">
         <v>45962</v>
@@ -3033,11 +3038,11 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G135">
-        <v>92.84</v>
+        <v>93.23</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -3047,18 +3052,23 @@
     </row>
     <row r="136">
       <c r="C136">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D136" s="1">
         <v>45962</v>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G136">
-        <v>9.06</v>
+        <v>14.04</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -3067,11 +3077,6 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisboa</t>
-        </is>
-      </c>
       <c r="C137">
         <v>15</v>
       </c>
@@ -3080,11 +3085,11 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">SALUD</t>
         </is>
       </c>
       <c r="G137">
-        <v>69.78</v>
+        <v>49.01</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -3094,18 +3099,18 @@
     </row>
     <row r="138">
       <c r="C138">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D138" s="1">
         <v>45962</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G138">
-        <v>28.34</v>
+        <v>20.72</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -3115,7 +3120,7 @@
     </row>
     <row r="139">
       <c r="C139">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D139" s="1">
         <v>45962</v>
@@ -3127,11 +3132,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G139">
-        <v>55.98</v>
+        <v>13.79</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -3140,19 +3145,24 @@
       </c>
     </row>
     <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Praga</t>
+        </is>
+      </c>
       <c r="C140">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D140" s="1">
         <v>45962</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G140">
-        <v>58.3</v>
+        <v>185.07</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -3161,19 +3171,24 @@
       </c>
     </row>
     <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C141">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D141" s="1">
         <v>45962</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G141">
-        <v>61.5</v>
+        <v>121.1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -3183,39 +3198,49 @@
     </row>
     <row r="142">
       <c r="C142">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D142" s="1">
         <v>45962</v>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G142">
-        <v>15.61</v>
+        <v>9.12</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet+celular</t>
+        </is>
+      </c>
       <c r="C143">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D143" s="1">
         <v>45962</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G143">
-        <v>63.38</v>
+        <v>34.53</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -3224,45 +3249,45 @@
       </c>
     </row>
     <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Psicóloga</t>
+        </is>
+      </c>
       <c r="C144">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D144" s="1">
         <v>45962</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G144">
-        <v>9.53</v>
+        <v>134.55</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C145">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D145" s="1">
         <v>45962</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G145">
-        <v>139.02</v>
+        <v>61.28</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -3272,18 +3297,23 @@
     </row>
     <row r="146">
       <c r="C146">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D146" s="1">
         <v>45962</v>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G146">
-        <v>90.92</v>
+        <v>16.51</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -3293,50 +3323,60 @@
     </row>
     <row r="147">
       <c r="C147">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D147" s="1">
         <v>45962</v>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G147">
-        <v>94.29</v>
+        <v>23.29</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="C148">
+        <v>10</v>
+      </c>
+      <c r="D148" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">otros</t>
+        </is>
+      </c>
+      <c r="G148">
+        <v>44.29</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Praga</t>
+        </is>
+      </c>
+      <c r="C149">
         <v>25</v>
       </c>
-      <c r="D148" s="1">
-        <v>45962</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>46.43</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="C149">
-        <v>27</v>
-      </c>
       <c r="D149" s="1">
         <v>45962</v>
       </c>
@@ -3347,11 +3387,11 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G149">
-        <v>15.02</v>
+        <v>103.41</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -3361,131 +3401,201 @@
     </row>
     <row r="150">
       <c r="C150">
+        <v>8</v>
+      </c>
+      <c r="D150" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transporte</t>
+        </is>
+      </c>
+      <c r="G150">
+        <v>26.09</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
+      <c r="C151">
         <v>17</v>
       </c>
-      <c r="D150" s="1">
-        <v>45962</v>
-      </c>
-      <c r="E150" t="inlineStr">
+      <c r="D151" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gastos fijos</t>
+        </is>
+      </c>
+      <c r="G151">
+        <v>125.39</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G152">
+        <v>12.07</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guanacaste</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>8</v>
+      </c>
+      <c r="D153" s="1">
+        <v>45962</v>
+      </c>
+      <c r="E153" t="inlineStr">
         <is>
           <t xml:space="preserve">detalle de ejemplo</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">regalos</t>
-        </is>
-      </c>
-      <c r="G150">
-        <v>385.35</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">i</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="C151">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">viajes</t>
+        </is>
+      </c>
+      <c r="G153">
+        <v>85.82</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154">
+        <v>8</v>
+      </c>
+      <c r="D154" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">supermercado</t>
+        </is>
+      </c>
+      <c r="G154">
+        <v>51.46</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155">
         <v>28</v>
       </c>
-      <c r="D151" s="1">
-        <v>45962</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="D155" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">entretenimiento</t>
+        </is>
+      </c>
+      <c r="G155">
+        <v>90.24</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156">
+        <v>26</v>
+      </c>
+      <c r="D156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
-      <c r="G151">
-        <v>11.98</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DICIEMBRE 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INGRESOS Y GASTOS</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GASTOS POR TIPO</t>
+      <c r="G156">
+        <v>18.65</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G/Acum./Mes</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comentarios</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DÍA</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MES</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETALLES</t>
-        </is>
+      <c r="C157">
+        <v>5</v>
+      </c>
+      <c r="D157" s="1">
+        <v>45962</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBRO</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MONTO</t>
-        </is>
+          <t xml:space="preserve">transporte</t>
+        </is>
+      </c>
+      <c r="G157">
+        <v>46.8</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">I/G</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="C158">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D158" s="1">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G158">
-        <v>65.13</v>
+        <v>21.56</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -3494,19 +3604,29 @@
       </c>
     </row>
     <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C159">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D159" s="1">
-        <v>45992</v>
+        <v>45962</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G159">
-        <v>23.97</v>
+        <v>44.42</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -3514,177 +3634,104 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="C160">
-        <v>27</v>
-      </c>
-      <c r="D160" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G160">
-        <v>8.22</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="C161">
-        <v>7</v>
-      </c>
-      <c r="D161" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G161">
-        <v>87.3</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
-      <c r="C162">
-        <v>30</v>
-      </c>
-      <c r="D162" s="1">
-        <v>45992</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">comida hecha</t>
-        </is>
-      </c>
-      <c r="G162">
-        <v>13.79</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="C163">
-        <v>20</v>
-      </c>
-      <c r="D163" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G163">
-        <v>46.99</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DICIEMBRE 2025</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="C164">
-        <v>27</v>
-      </c>
-      <c r="D164" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G164">
-        <v>65.91</v>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGRESOS Y GASTOS</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GASTOS POR TIPO</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="C165">
-        <v>14</v>
-      </c>
-      <c r="D165" s="1">
-        <v>45992</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G/Acum./Mes</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comentarios</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DÍA</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MES</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETALLES</t>
+        </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
-        </is>
-      </c>
-      <c r="G165">
-        <v>41.56</v>
+          <t xml:space="preserve">RUBRO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONTO</t>
+        </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I/G</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="C166">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D166" s="1">
         <v>45992</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G166">
-        <v>57.23</v>
+        <v>1997.37</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">i</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="B167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guanacaste</t>
-        </is>
-      </c>
       <c r="C167">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D167" s="1">
         <v>45992</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G167">
-        <v>45.26</v>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11,19</t>
+        </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -3694,7 +3741,7 @@
     </row>
     <row r="168">
       <c r="C168">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D168" s="1">
         <v>45992</v>
@@ -3705,7 +3752,7 @@
         </is>
       </c>
       <c r="G168">
-        <v>15.63</v>
+        <v>58.07202222434432</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -3715,28 +3762,30 @@
     </row>
     <row r="169">
       <c r="C169">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D169" s="1">
         <v>45992</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G169">
-        <v>62.15</v>
+          <t xml:space="preserve">regalos</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1919,97</t>
+        </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="C170">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D170" s="1">
         <v>45992</v>
@@ -3747,7 +3796,7 @@
         </is>
       </c>
       <c r="G170">
-        <v>94.84</v>
+        <v>70.05</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -3756,71 +3805,68 @@
       </c>
     </row>
     <row r="171">
-      <c r="B171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C171">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D171" s="1">
         <v>45992</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G171">
-        <v>138.97</v>
+        <v>33.89</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisboa</t>
+        </is>
+      </c>
       <c r="C172">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D172" s="1">
         <v>45992</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">trabajo</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G172">
-        <v>1535.14</v>
+        <v>39.44</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="B173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Praga</t>
-        </is>
-      </c>
       <c r="C173">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D173" s="1">
         <v>45992</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G173">
-        <v>178.91</v>
+          <t xml:space="preserve">comida hecha</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6,39</t>
+        </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -3830,23 +3876,18 @@
     </row>
     <row r="174">
       <c r="C174">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D174" s="1">
         <v>45992</v>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G174">
-        <v>36.83</v>
+        <v>13.93</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -3855,6 +3896,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C175">
         <v>17</v>
       </c>
@@ -3868,11 +3914,11 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">VIAJES</t>
         </is>
       </c>
       <c r="G175">
-        <v>58.01</v>
+        <v>242.91</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -3882,49 +3928,39 @@
     </row>
     <row r="176">
       <c r="C176">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D176" s="1">
         <v>45992</v>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G176">
-        <v>87.6</v>
+        <v>38.98</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="C177">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D177" s="1">
         <v>45992</v>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G177">
-        <v>72.26</v>
+        <v>58.6</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -3934,23 +3970,18 @@
     </row>
     <row r="178">
       <c r="C178">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D178" s="1">
         <v>45992</v>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G178">
-        <v>34.02</v>
+        <v>11.11</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -3960,23 +3991,18 @@
     </row>
     <row r="179">
       <c r="C179">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D179" s="1">
         <v>45992</v>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G179">
-        <v>30.5</v>
+        <v>44.1893484164911</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -3985,45 +4011,40 @@
       </c>
     </row>
     <row r="180">
-      <c r="B180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
       <c r="C180">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D180" s="1">
         <v>45992</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G180">
-        <v>170.22</v>
+        <v>53.79</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="C181">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D181" s="1">
         <v>45992</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G181">
-        <v>44.67</v>
+        <v>50.41</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -4033,39 +4054,46 @@
     </row>
     <row r="182">
       <c r="C182">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D182" s="1">
         <v>45992</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G182">
-        <v>36.69</v>
+        <v>691.41</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="C183">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D183" s="1">
         <v>45992</v>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G183">
-        <v>17.49</v>
+          <t xml:space="preserve">transporte</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91,72</t>
+        </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -4074,24 +4102,19 @@
       </c>
     </row>
     <row r="184">
-      <c r="B184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atenas</t>
-        </is>
-      </c>
       <c r="C184">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D184" s="1">
         <v>45992</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G184">
-        <v>207.31</v>
+        <v>80.88</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -4100,19 +4123,29 @@
       </c>
     </row>
     <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisboa</t>
+        </is>
+      </c>
       <c r="C185">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D185" s="1">
         <v>45992</v>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G185">
-        <v>10.15</v>
+        <v>29.19</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -4123,11 +4156,11 @@
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luz</t>
+          <t xml:space="preserve">Roma</t>
         </is>
       </c>
       <c r="C186">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D186" s="1">
         <v>45992</v>
@@ -4139,58 +4172,63 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G186">
-        <v>95.84</v>
+        <v>192.8519526952188</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atenas</t>
+        </is>
+      </c>
       <c r="C187">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D187" s="1">
         <v>45992</v>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G187">
-        <v>22.21</v>
+        <v>240.06</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="C188">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D188" s="1">
         <v>45992</v>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G188">
-        <v>16.87</v>
+        <v>123.02</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -4200,44 +4238,39 @@
     </row>
     <row r="189">
       <c r="C189">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D189" s="1">
         <v>45992</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G189">
-        <v>58.07</v>
+        <v>57.71</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="B190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
       <c r="C190">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D190" s="1">
         <v>45992</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G190">
-        <v>93.88</v>
+        <v>38.67</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -4247,18 +4280,18 @@
     </row>
     <row r="191">
       <c r="C191">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D191" s="1">
         <v>45992</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G191">
-        <v>70.05</v>
+        <v>88</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -4268,18 +4301,18 @@
     </row>
     <row r="192">
       <c r="C192">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D192" s="1">
         <v>45992</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G192">
-        <v>57.31</v>
+        <v>85.31</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -4288,50 +4321,45 @@
       </c>
     </row>
     <row r="193">
-      <c r="B193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gas</t>
-        </is>
-      </c>
       <c r="C193">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D193" s="1">
         <v>45992</v>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">SALUD</t>
         </is>
       </c>
       <c r="G193">
-        <v>32.98</v>
+        <v>81.04</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
       <c r="C194">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D194" s="1">
         <v>45992</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G194">
-        <v>27.22</v>
+        <v>36.95</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -4342,22 +4370,22 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa</t>
+          <t xml:space="preserve">Praga</t>
         </is>
       </c>
       <c r="C195">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D195" s="1">
         <v>45992</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">VIAJES</t>
         </is>
       </c>
       <c r="G195">
-        <v>219.73</v>
+        <v>213.89</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -4367,49 +4395,44 @@
     </row>
     <row r="196">
       <c r="C196">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D196" s="1">
         <v>45992</v>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G196">
-        <v>53.33</v>
+        <v>585.52</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="B197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
       <c r="C197">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D197" s="1">
         <v>45992</v>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G197">
-        <v>86.28</v>
+        <v>19.715932791920345</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -4418,19 +4441,24 @@
       </c>
     </row>
     <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
       <c r="C198">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D198" s="1">
         <v>45992</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G198">
-        <v>46.55</v>
+        <v>62.48</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -4439,19 +4467,24 @@
       </c>
     </row>
     <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
       <c r="C199">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D199" s="1">
         <v>45992</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G199">
-        <v>40.79</v>
+        <v>181.08</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -4460,40 +4493,50 @@
       </c>
     </row>
     <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atenas</t>
+        </is>
+      </c>
       <c r="C200">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D200" s="1">
         <v>45992</v>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G200">
-        <v>48.32</v>
+        <v>48.79</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="C201">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D201" s="1">
         <v>45992</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G201">
-        <v>50.8</v>
+        <v>65.96</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -4503,18 +4546,18 @@
     </row>
     <row r="202">
       <c r="C202">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D202" s="1">
         <v>45992</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G202">
-        <v>53.79</v>
+        <v>57.93</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -4524,18 +4567,18 @@
     </row>
     <row r="203">
       <c r="C203">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D203" s="1">
         <v>45992</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G203">
-        <v>76.04</v>
+        <v>52.16</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -4545,18 +4588,18 @@
     </row>
     <row r="204">
       <c r="C204">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D204" s="1">
         <v>45992</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G204">
-        <v>6.34</v>
+        <v>14.87</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -4565,19 +4608,24 @@
       </c>
     </row>
     <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Praga</t>
+        </is>
+      </c>
       <c r="C205">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D205" s="1">
         <v>45992</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G205">
-        <v>70.22</v>
+        <v>75.05725267345889</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -4587,23 +4635,18 @@
     </row>
     <row r="206">
       <c r="C206">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D206" s="1">
         <v>45992</v>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G206">
-        <v>29.75</v>
+        <v>136.08</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -4612,24 +4655,24 @@
       </c>
     </row>
     <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas</t>
+        </is>
+      </c>
       <c r="C207">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D207" s="1">
         <v>45992</v>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G207">
-        <v>28.6</v>
+        <v>116.19</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -4639,75 +4682,60 @@
     </row>
     <row r="208">
       <c r="C208">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D208" s="1">
         <v>45992</v>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">trabajo</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G208">
-        <v>330.23</v>
+        <v>26.43</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="B209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
       <c r="C209">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D209" s="1">
         <v>45992</v>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G209">
-        <v>192.85</v>
+        <v>68.14</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="C210">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D210" s="1">
         <v>45992</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G210">
-        <v>47.17</v>
+        <v>77.25068572547784</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -4716,50 +4744,45 @@
       </c>
     </row>
     <row r="211">
-      <c r="B211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C211">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D211" s="1">
         <v>45992</v>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G211">
-        <v>27.19</v>
+        <v>14.51</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="C212">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D212" s="1">
         <v>45992</v>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G212">
-        <v>14.84</v>
+        <v>11.12</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -4769,7 +4792,7 @@
     </row>
     <row r="213">
       <c r="C213">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D213" s="1">
         <v>45992</v>
@@ -4781,11 +4804,11 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G213">
-        <v>28.42</v>
+        <v>77.18</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -4794,24 +4817,19 @@
       </c>
     </row>
     <row r="214">
-      <c r="B214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internet+celular</t>
-        </is>
-      </c>
       <c r="C214">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D214" s="1">
         <v>45992</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G214">
-        <v>56.67</v>
+        <v>39.09</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -4821,18 +4839,18 @@
     </row>
     <row r="215">
       <c r="C215">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D215" s="1">
         <v>45992</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G215">
-        <v>20.34</v>
+        <v>39.2337525050313</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -4842,39 +4860,39 @@
     </row>
     <row r="216">
       <c r="C216">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D216" s="1">
         <v>45992</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G216">
-        <v>85.22</v>
+        <v>621.6043951090446</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="C217">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D217" s="1">
         <v>45992</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G217">
-        <v>8.89</v>
+        <v>4.31</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -4884,23 +4902,18 @@
     </row>
     <row r="218">
       <c r="C218">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D218" s="1">
         <v>45992</v>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G218">
-        <v>23.37</v>
+        <v>62.36</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -4910,18 +4923,18 @@
     </row>
     <row r="219">
       <c r="C219">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D219" s="1">
         <v>45992</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G219">
-        <v>17.05</v>
+        <v>107.78</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -4931,65 +4944,70 @@
     </row>
     <row r="220">
       <c r="C220">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D220" s="1">
         <v>45992</v>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G220">
-        <v>507.74</v>
+        <v>91.16</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="C221">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D221" s="1">
         <v>45992</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">regalos</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G221">
-        <v>1443.48</v>
+        <v>50.92</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coruña</t>
+          <t xml:space="preserve">Gas</t>
         </is>
       </c>
       <c r="C222">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D222" s="1">
         <v>45992</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G222">
-        <v>23.89</v>
+        <v>41.21</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -4998,24 +5016,19 @@
       </c>
     </row>
     <row r="223">
-      <c r="B223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
       <c r="C223">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D223" s="1">
         <v>45992</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">SUPERMERCADO</t>
         </is>
       </c>
       <c r="G223">
-        <v>52.41</v>
+        <v>51.98331852815268</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -5024,24 +5037,19 @@
       </c>
     </row>
     <row r="224">
-      <c r="B224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guanacaste</t>
-        </is>
-      </c>
       <c r="C224">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D224" s="1">
         <v>45992</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G224">
-        <v>105.62</v>
+        <v>24.82</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -5050,29 +5058,19 @@
       </c>
     </row>
     <row r="225">
-      <c r="B225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atenas</t>
-        </is>
-      </c>
       <c r="C225">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D225" s="1">
         <v>45992</v>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G225">
-        <v>48.79</v>
+        <v>19.84</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -5080,143 +5078,78 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="C226">
-        <v>3</v>
-      </c>
-      <c r="D226" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G226">
-        <v>64.02</v>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="C227">
-        <v>13</v>
-      </c>
-      <c r="D227" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G227">
-        <v>121.6</v>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
     <row r="228">
-      <c r="C228">
-        <v>11</v>
-      </c>
-      <c r="D228" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">transporte</t>
-        </is>
-      </c>
-      <c r="G228">
-        <v>69.56</v>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="C229">
-        <v>9</v>
-      </c>
-      <c r="D229" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G229">
-        <v>22.31</v>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENERO 2026</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="C230">
-        <v>22</v>
-      </c>
-      <c r="D230" s="1">
-        <v>45992</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G230">
-        <v>65.38</v>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INGRESOS Y GASTOS</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GASTOS POR TIPO</t>
         </is>
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G/Acum./Mes</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
-      <c r="C231">
-        <v>22</v>
-      </c>
-      <c r="D231" s="1">
-        <v>45992</v>
+          <t xml:space="preserve">Comentarios</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DÍA</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MES</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETALLES</t>
+        </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G231">
-        <v>27.33</v>
+          <t xml:space="preserve">RUBRO</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONTO</t>
+        </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I/G</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="C232">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D232" s="1">
-        <v>45992</v>
+        <v>46023</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -5224,54 +5157,49 @@
         </is>
       </c>
       <c r="G232">
-        <v>54.32</v>
+        <v>12.34</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="B233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gas</t>
-        </is>
-      </c>
       <c r="C233">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D233" s="1">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G233">
-        <v>116.19</v>
+        <v>1352.67</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="C234">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D234" s="1">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G234">
-        <v>26.29</v>
+        <v>17.41</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -5281,10 +5209,10 @@
     </row>
     <row r="235">
       <c r="C235">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D235" s="1">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5293,11 +5221,11 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G235">
-        <v>81.31</v>
+        <v>66.93</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -5307,18 +5235,23 @@
     </row>
     <row r="236">
       <c r="C236">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D236" s="1">
-        <v>45992</v>
+        <v>46023</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G236">
-        <v>36.4</v>
+        <v>8.08</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -5326,81 +5259,178 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="C237">
+        <v>5</v>
+      </c>
+      <c r="D237" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inversiones</t>
+        </is>
+      </c>
+      <c r="G237">
+        <v>438.94</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>8</v>
+      </c>
+      <c r="D238" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">viajes</t>
+        </is>
+      </c>
+      <c r="G238">
+        <v>83.08</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENERO 2026</t>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guanacaste</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>18</v>
+      </c>
+      <c r="D239" s="1">
+        <v>46023</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIAJES</t>
+        </is>
+      </c>
+      <c r="G239">
+        <v>28.34</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>25</v>
+      </c>
+      <c r="D240" s="1">
+        <v>46023</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">viajes</t>
+        </is>
+      </c>
+      <c r="G240">
+        <v>157.88</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INGRESOS Y GASTOS</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GASTOS POR TIPO</t>
+      <c r="C241">
+        <v>18</v>
+      </c>
+      <c r="D241" s="1">
+        <v>46023</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regalos</t>
+        </is>
+      </c>
+      <c r="G241">
+        <v>872.32</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G/Acum./Mes</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comentarios</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DÍA</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MES</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETALLES</t>
-        </is>
+      <c r="C242">
+        <v>10</v>
+      </c>
+      <c r="D242" s="1">
+        <v>46023</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBRO</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MONTO</t>
-        </is>
+          <t xml:space="preserve">gastos fijos</t>
+        </is>
+      </c>
+      <c r="G242">
+        <v>81.75653937354524</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">I/G</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="C243">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D243" s="1">
         <v>46023</v>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">inversiones</t>
-        </is>
-      </c>
-      <c r="G243">
-        <v>340.08</v>
+          <t xml:space="preserve">regalos</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918,65</t>
+        </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -5409,45 +5439,45 @@
       </c>
     </row>
     <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roma</t>
+        </is>
+      </c>
       <c r="C244">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D244" s="1">
         <v>46023</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G244">
-        <v>87.97</v>
+        <v>34.94</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="B245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
       <c r="C245">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D245" s="1">
         <v>46023</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G245">
-        <v>214.07</v>
+        <v>88.52</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -5456,8 +5486,13 @@
       </c>
     </row>
     <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet+celular</t>
+        </is>
+      </c>
       <c r="C246">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D246" s="1">
         <v>46023</v>
@@ -5469,11 +5504,11 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G246">
-        <v>87.61</v>
+        <v>111.48</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -5482,24 +5517,19 @@
       </c>
     </row>
     <row r="247">
-      <c r="B247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coruña</t>
-        </is>
-      </c>
       <c r="C247">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D247" s="1">
         <v>46023</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G247">
-        <v>101.24</v>
+        <v>48.66</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -5509,23 +5539,18 @@
     </row>
     <row r="248">
       <c r="C248">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D248" s="1">
         <v>46023</v>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G248">
-        <v>92.75</v>
+        <v>92.97</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -5534,19 +5559,24 @@
       </c>
     </row>
     <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet+celular</t>
+        </is>
+      </c>
       <c r="C249">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D249" s="1">
         <v>46023</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERMERCADO</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G249">
-        <v>48.08</v>
+        <v>34.55</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -5556,18 +5586,23 @@
     </row>
     <row r="250">
       <c r="C250">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D250" s="1">
         <v>46023</v>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G250">
-        <v>4.31</v>
+        <v>37.657137407761596</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -5584,37 +5619,32 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G251">
-        <v>55.91</v>
+        <v>2135.79</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="B252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guanacaste</t>
-        </is>
-      </c>
       <c r="C252">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D252" s="1">
         <v>46023</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G252">
-        <v>38.02</v>
+        <v>12.006510142239978</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -5623,24 +5653,21 @@
       </c>
     </row>
     <row r="253">
-      <c r="B253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roma</t>
-        </is>
-      </c>
       <c r="C253">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D253" s="1">
         <v>46023</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G253">
-        <v>148.22</v>
+          <t xml:space="preserve">entretenimiento</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85</t>
+        </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -5650,18 +5677,18 @@
     </row>
     <row r="254">
       <c r="C254">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D254" s="1">
         <v>46023</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G254">
-        <v>49.21</v>
+        <v>20.31</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -5671,23 +5698,18 @@
     </row>
     <row r="255">
       <c r="C255">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D255" s="1">
         <v>46023</v>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G255">
-        <v>48.29</v>
+        <v>11.32</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -5697,18 +5719,18 @@
     </row>
     <row r="256">
       <c r="C256">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D256" s="1">
         <v>46023</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G256">
-        <v>39.81</v>
+        <v>5.57</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -5717,40 +5739,45 @@
       </c>
     </row>
     <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
       <c r="C257">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D257" s="1">
         <v>46023</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERMERCADO</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G257">
-        <v>51.98</v>
+        <v>188.96</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="C258">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D258" s="1">
         <v>46023</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G258">
-        <v>13.33</v>
+        <v>75.13</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -5760,39 +5787,44 @@
     </row>
     <row r="259">
       <c r="C259">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D259" s="1">
         <v>46023</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">trabajo</t>
         </is>
       </c>
       <c r="G259">
-        <v>12.89</v>
+        <v>1551.25</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
       <c r="C260">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D260" s="1">
         <v>46023</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G260">
-        <v>21.41</v>
+        <v>80.02</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -5802,7 +5834,7 @@
     </row>
     <row r="261">
       <c r="C261">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D261" s="1">
         <v>46023</v>
@@ -5814,11 +5846,11 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G261">
-        <v>44.33</v>
+        <v>59.03</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -5829,22 +5861,22 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roma</t>
+          <t xml:space="preserve">Psicóloga</t>
         </is>
       </c>
       <c r="C262">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D262" s="1">
         <v>46023</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G262">
-        <v>148.06</v>
+        <v>74.99</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -5853,19 +5885,24 @@
       </c>
     </row>
     <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Psicóloga</t>
+        </is>
+      </c>
       <c r="C263">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D263" s="1">
         <v>46023</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">salud</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G263">
-        <v>26.4</v>
+        <v>99.74</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -5875,44 +5912,39 @@
     </row>
     <row r="264">
       <c r="C264">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D264" s="1">
         <v>46023</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G264">
-        <v>23.56</v>
+        <v>1541.1862856434593</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="C265">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D265" s="1">
         <v>46023</v>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G265">
-        <v>8.08</v>
+        <v>69.5</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -5923,26 +5955,26 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luz</t>
+          <t xml:space="preserve">Atenas</t>
         </is>
       </c>
       <c r="C266">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D266" s="1">
         <v>46023</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">gastos fijos</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G266">
-        <v>22.83</v>
+        <v>80.45</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">g</t>
         </is>
       </c>
     </row>
@@ -5953,23 +5985,18 @@
         </is>
       </c>
       <c r="C267">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D267" s="1">
         <v>46023</v>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F267" t="inlineStr">
         <is>
           <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G267">
-        <v>83.08</v>
+        <v>80.21</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -5979,39 +6006,39 @@
     </row>
     <row r="268">
       <c r="C268">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D268" s="1">
         <v>46023</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">otros</t>
         </is>
       </c>
       <c r="G268">
-        <v>39.23</v>
+        <v>1058.48</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="C269">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D269" s="1">
         <v>46023</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G269">
-        <v>62.25</v>
+        <v>12.28</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -6020,19 +6047,24 @@
       </c>
     </row>
     <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisboa</t>
+        </is>
+      </c>
       <c r="C270">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D270" s="1">
         <v>46023</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G270">
-        <v>88.48</v>
+        <v>104.95891273485445</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -6042,23 +6074,18 @@
     </row>
     <row r="271">
       <c r="C271">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D271" s="1">
         <v>46023</v>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G271">
-        <v>71.23</v>
+        <v>36.59</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -6068,60 +6095,65 @@
     </row>
     <row r="272">
       <c r="C272">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D272" s="1">
         <v>46023</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">COMIDA HECHA</t>
         </is>
       </c>
       <c r="G272">
-        <v>1229.28</v>
+        <v>9.01</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">i</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="C273">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D273" s="1">
         <v>46023</v>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">trabajo</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G273">
-        <v>1399.65</v>
+        <v>26.83</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="C274">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D274" s="1">
         <v>46023</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G274">
-        <v>71.61</v>
+        <v>65.7</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -6131,39 +6163,39 @@
     </row>
     <row r="275">
       <c r="C275">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D275" s="1">
         <v>46023</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">supermercado</t>
         </is>
       </c>
       <c r="G275">
-        <v>236.85</v>
+        <v>25.15</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="C276">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D276" s="1">
         <v>46023</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">salud</t>
         </is>
       </c>
       <c r="G276">
-        <v>82.82</v>
+        <v>22.863994845125823</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -6173,23 +6205,18 @@
     </row>
     <row r="277">
       <c r="C277">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D277" s="1">
         <v>46023</v>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G277">
-        <v>73.61</v>
+        <v>71.64613488439757</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -6198,24 +6225,19 @@
       </c>
     </row>
     <row r="278">
-      <c r="B278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atenas</t>
-        </is>
-      </c>
       <c r="C278">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D278" s="1">
         <v>46023</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G278">
-        <v>136.27</v>
+        <v>14.04</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -6225,18 +6247,18 @@
     </row>
     <row r="279">
       <c r="C279">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D279" s="1">
         <v>46023</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G279">
-        <v>21.87</v>
+        <v>34.79</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -6246,23 +6268,18 @@
     </row>
     <row r="280">
       <c r="C280">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D280" s="1">
         <v>46023</v>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">entretenimiento</t>
         </is>
       </c>
       <c r="G280">
-        <v>28.76</v>
+        <v>92.69</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -6272,23 +6289,20 @@
     </row>
     <row r="281">
       <c r="C281">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D281" s="1">
         <v>46023</v>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
-        </is>
-      </c>
-      <c r="G281">
-        <v>22.37</v>
+          <t xml:space="preserve">TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33,82</t>
+        </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -6298,86 +6312,91 @@
     </row>
     <row r="282">
       <c r="C282">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D282" s="1">
         <v>46023</v>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">supermercado</t>
+          <t xml:space="preserve">inversiones</t>
         </is>
       </c>
       <c r="G282">
-        <v>75.84</v>
+        <v>834.54</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="C283">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D283" s="1">
         <v>46023</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">otros</t>
+          <t xml:space="preserve">transporte</t>
         </is>
       </c>
       <c r="G283">
-        <v>1795.74</v>
+        <v>86.89</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
       <c r="C284">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D284" s="1">
         <v>46023</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G284">
-        <v>12.01</v>
+        <v>93.84</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luz</t>
+        </is>
+      </c>
       <c r="C285">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D285" s="1">
         <v>46023</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">comida hecha</t>
+          <t xml:space="preserve">gastos fijos</t>
         </is>
       </c>
       <c r="G285">
-        <v>16.88</v>
+        <v>65.64899765218095</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -6386,19 +6405,29 @@
       </c>
     </row>
     <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coruña</t>
+        </is>
+      </c>
       <c r="C286">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D286" s="1">
         <v>46023</v>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">entretenimiento</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G286">
-        <v>87.92</v>
+        <v>35.2</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -6408,65 +6437,62 @@
     </row>
     <row r="287">
       <c r="C287">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D287" s="1">
         <v>46023</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">regalos</t>
         </is>
       </c>
       <c r="G287">
-        <v>12.33</v>
+        <v>1327.63</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="C288">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D288" s="1">
         <v>46023</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">inversiones</t>
+          <t xml:space="preserve">comida hecha</t>
         </is>
       </c>
       <c r="G288">
-        <v>1659.96</v>
+        <v>9.57</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="B289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Praga</t>
-        </is>
-      </c>
       <c r="C289">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D289" s="1">
         <v>46023</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G289">
-        <v>75.8</v>
+          <t xml:space="preserve">salud</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92,52</t>
+        </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -6475,507 +6501,31 @@
       </c>
     </row>
     <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atenas</t>
+        </is>
+      </c>
       <c r="C290">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D290" s="1">
         <v>46023</v>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detalle de ejemplo</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">transporte</t>
+          <t xml:space="preserve">viajes</t>
         </is>
       </c>
       <c r="G290">
-        <v>43.11</v>
+        <v>236.3</v>
       </c>
       <c r="H290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="C291">
-        <v>8</v>
-      </c>
-      <c r="D291" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salud</t>
-        </is>
-      </c>
-      <c r="G291">
-        <v>90.34</v>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="C292">
-        <v>2</v>
-      </c>
-      <c r="D292" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">trabajo</t>
-        </is>
-      </c>
-      <c r="G292">
-        <v>1551.25</v>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="C293">
-        <v>5</v>
-      </c>
-      <c r="D293" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">supermercado</t>
-        </is>
-      </c>
-      <c r="G293">
-        <v>16.59</v>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="C294">
-        <v>24</v>
-      </c>
-      <c r="D294" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">comida hecha</t>
-        </is>
-      </c>
-      <c r="G294">
-        <v>28.18</v>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="C295">
-        <v>19</v>
-      </c>
-      <c r="D295" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G295">
-        <v>60.58</v>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="C296">
-        <v>3</v>
-      </c>
-      <c r="D296" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G296">
-        <v>46.25</v>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="C297">
-        <v>27</v>
-      </c>
-      <c r="D297" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G297">
-        <v>12.42</v>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="B298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisboa</t>
-        </is>
-      </c>
-      <c r="C298">
-        <v>29</v>
-      </c>
-      <c r="D298" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">viajes</t>
-        </is>
-      </c>
-      <c r="G298">
-        <v>160.76</v>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="C299">
-        <v>30</v>
-      </c>
-      <c r="D299" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G299">
-        <v>32.9</v>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="C300">
-        <v>17</v>
-      </c>
-      <c r="D300" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salud</t>
-        </is>
-      </c>
-      <c r="G300">
-        <v>62.55</v>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="C301">
-        <v>30</v>
-      </c>
-      <c r="D301" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMIDA HECHA</t>
-        </is>
-      </c>
-      <c r="G301">
-        <v>12.55</v>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="C302">
-        <v>10</v>
-      </c>
-      <c r="D302" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">comida hecha</t>
-        </is>
-      </c>
-      <c r="G302">
-        <v>10.52</v>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="C303">
-        <v>26</v>
-      </c>
-      <c r="D303" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G303">
-        <v>71.51</v>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="C304">
-        <v>7</v>
-      </c>
-      <c r="D304" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">comida hecha</t>
-        </is>
-      </c>
-      <c r="G304">
-        <v>11.47</v>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="C305">
-        <v>29</v>
-      </c>
-      <c r="D305" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="G305">
-        <v>37.57</v>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psicóloga</t>
-        </is>
-      </c>
-      <c r="C306">
-        <v>10</v>
-      </c>
-      <c r="D306" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G306">
-        <v>73.86</v>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="C307">
-        <v>26</v>
-      </c>
-      <c r="D307" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gastos fijos</t>
-        </is>
-      </c>
-      <c r="G307">
-        <v>63.16</v>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="C308">
-        <v>2</v>
-      </c>
-      <c r="D308" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G308">
-        <v>83.21</v>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="C309">
-        <v>7</v>
-      </c>
-      <c r="D309" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">otros</t>
-        </is>
-      </c>
-      <c r="G309">
-        <v>16.1</v>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="C310">
-        <v>21</v>
-      </c>
-      <c r="D310" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detalle de ejemplo</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G310">
-        <v>94.87</v>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="C311">
-        <v>6</v>
-      </c>
-      <c r="D311" s="1">
-        <v>46023</v>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entretenimiento</t>
-        </is>
-      </c>
-      <c r="G311">
-        <v>27</v>
-      </c>
-      <c r="H311" t="inlineStr">
         <is>
           <t xml:space="preserve">G</t>
         </is>
